--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/77.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/77.xlsx
@@ -426,13 +426,13 @@
         <v>-6.222834635396652</v>
       </c>
       <c r="E2">
-        <v>-9.089414722209305</v>
+        <v>-7.477436472068927</v>
       </c>
       <c r="F2">
-        <v>-7.371542674855673</v>
+        <v>-7.514232687641201</v>
       </c>
       <c r="G2">
-        <v>-9.778935544937472</v>
+        <v>-8.422164734941344</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.564412518666804</v>
       </c>
       <c r="E3">
-        <v>-9.671133436286624</v>
+        <v>-9.207789032769808</v>
       </c>
       <c r="F3">
-        <v>-7.437590064615684</v>
+        <v>-7.387870210548553</v>
       </c>
       <c r="G3">
-        <v>-8.805486181842475</v>
+        <v>-8.637906366644568</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-7.01557649186448</v>
       </c>
       <c r="E4">
-        <v>-10.16295288436367</v>
+        <v>-8.097325693556899</v>
       </c>
       <c r="F4">
-        <v>-7.77810208268006</v>
+        <v>-7.425875706988995</v>
       </c>
       <c r="G4">
-        <v>-9.351782475096389</v>
+        <v>-8.802817882137823</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.503430192422583</v>
       </c>
       <c r="E5">
-        <v>-12.45674270957291</v>
+        <v>-9.811122153285739</v>
       </c>
       <c r="F5">
-        <v>-7.251134088470647</v>
+        <v>-7.310691219629724</v>
       </c>
       <c r="G5">
-        <v>-9.121471132474833</v>
+        <v>-8.614047264943041</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.001597254414248</v>
       </c>
       <c r="E6">
-        <v>-12.17545201811246</v>
+        <v>-10.63808490572245</v>
       </c>
       <c r="F6">
-        <v>-7.501104306857934</v>
+        <v>-7.220248409857268</v>
       </c>
       <c r="G6">
-        <v>-9.580193564578405</v>
+        <v>-8.31807456209558</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.465241840762047</v>
       </c>
       <c r="E7">
-        <v>-13.84571172873155</v>
+        <v>-11.75426317913304</v>
       </c>
       <c r="F7">
-        <v>-7.150135392884318</v>
+        <v>-7.007765129916271</v>
       </c>
       <c r="G7">
-        <v>-8.53542511893089</v>
+        <v>-8.305514352319584</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.855904623959606</v>
       </c>
       <c r="E8">
-        <v>-13.20300352671893</v>
+        <v>-12.78963536235076</v>
       </c>
       <c r="F8">
-        <v>-6.960416063355953</v>
+        <v>-7.06908958292922</v>
       </c>
       <c r="G8">
-        <v>-9.034330952790135</v>
+        <v>-8.177525351225821</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-9.147429006651459</v>
       </c>
       <c r="E9">
-        <v>-14.43845727701755</v>
+        <v>-13.10525188678936</v>
       </c>
       <c r="F9">
-        <v>-7.269143624174911</v>
+        <v>-6.979356684020964</v>
       </c>
       <c r="G9">
-        <v>-9.9394274821358</v>
+        <v>-7.76771622946498</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-9.318018050043857</v>
       </c>
       <c r="E10">
-        <v>-16.65760879363236</v>
+        <v>-13.2064723378088</v>
       </c>
       <c r="F10">
-        <v>-7.114022301775572</v>
+        <v>-6.893599948646144</v>
       </c>
       <c r="G10">
-        <v>-9.016695676702438</v>
+        <v>-7.523626396308976</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.361016694628944</v>
       </c>
       <c r="E11">
-        <v>-16.36561278961777</v>
+        <v>-15.26516190643583</v>
       </c>
       <c r="F11">
-        <v>-6.707807080607049</v>
+        <v>-6.956045596938782</v>
       </c>
       <c r="G11">
-        <v>-8.345909628989771</v>
+        <v>-7.42158876169756</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.282132202198907</v>
       </c>
       <c r="E12">
-        <v>-16.40853366626247</v>
+        <v>-15.3694119065664</v>
       </c>
       <c r="F12">
-        <v>-6.792269077731292</v>
+        <v>-6.899287105050064</v>
       </c>
       <c r="G12">
-        <v>-8.417596182097149</v>
+        <v>-6.689789359696125</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.088828516391517</v>
       </c>
       <c r="E13">
-        <v>-16.92382872359529</v>
+        <v>-16.03925925330699</v>
       </c>
       <c r="F13">
-        <v>-6.587169450635148</v>
+        <v>-6.831215599541314</v>
       </c>
       <c r="G13">
-        <v>-8.87683174875931</v>
+        <v>-6.845328720767703</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.8063645992725</v>
       </c>
       <c r="E14">
-        <v>-17.86992204175179</v>
+        <v>-17.16274648376596</v>
       </c>
       <c r="F14">
-        <v>-5.972940820031135</v>
+        <v>-6.258244635801132</v>
       </c>
       <c r="G14">
-        <v>-8.41114392884111</v>
+        <v>-6.028656862775972</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.453772869968962</v>
       </c>
       <c r="E15">
-        <v>-19.10996766469418</v>
+        <v>-17.73985973977748</v>
       </c>
       <c r="F15">
-        <v>-6.317023101601577</v>
+        <v>-6.314188428349197</v>
       </c>
       <c r="G15">
-        <v>-7.887054775064628</v>
+        <v>-5.541258485211232</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-8.0590677637159</v>
       </c>
       <c r="E16">
-        <v>-19.78409441937202</v>
+        <v>-19.62034027078065</v>
       </c>
       <c r="F16">
-        <v>-5.733402646531005</v>
+        <v>-5.920700658140986</v>
       </c>
       <c r="G16">
-        <v>-7.057663801111017</v>
+        <v>-5.399471130309786</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.649865909344324</v>
       </c>
       <c r="E17">
-        <v>-20.11571909942773</v>
+        <v>-20.11571004247971</v>
       </c>
       <c r="F17">
-        <v>-6.09373666817697</v>
+        <v>-6.053736463030587</v>
       </c>
       <c r="G17">
-        <v>-7.020135456877839</v>
+        <v>-4.635023128200059</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-7.245849883422086</v>
       </c>
       <c r="E18">
-        <v>-22.03057980509713</v>
+        <v>-21.03119993329237</v>
       </c>
       <c r="F18">
-        <v>-5.31937219310077</v>
+        <v>-5.474540318258367</v>
       </c>
       <c r="G18">
-        <v>-6.779948756912636</v>
+        <v>-4.952775910150386</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.876553920950786</v>
       </c>
       <c r="E19">
-        <v>-22.07311123297717</v>
+        <v>-21.78240131558077</v>
       </c>
       <c r="F19">
-        <v>-5.292113935344249</v>
+        <v>-5.472698029154541</v>
       </c>
       <c r="G19">
-        <v>-6.217463895971687</v>
+        <v>-4.526188943596519</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.556346154775889</v>
       </c>
       <c r="E20">
-        <v>-23.45631097625004</v>
+        <v>-22.93821279350649</v>
       </c>
       <c r="F20">
-        <v>-4.867356952415164</v>
+        <v>-5.324590079371004</v>
       </c>
       <c r="G20">
-        <v>-6.009247134279225</v>
+        <v>-4.621969647138712</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-6.304833385405898</v>
       </c>
       <c r="E21">
-        <v>-24.14268272464463</v>
+        <v>-23.73402870171844</v>
       </c>
       <c r="F21">
-        <v>-4.283097826077033</v>
+        <v>-4.639447400515532</v>
       </c>
       <c r="G21">
-        <v>-6.23211968107404</v>
+        <v>-4.487280101873464</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.131674995260858</v>
       </c>
       <c r="E22">
-        <v>-24.97125308535406</v>
+        <v>-25.04165274227731</v>
       </c>
       <c r="F22">
-        <v>-4.137159370521427</v>
+        <v>-4.569403966404417</v>
       </c>
       <c r="G22">
-        <v>-7.52924439208912</v>
+        <v>-4.643746415696039</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.031761058643104</v>
       </c>
       <c r="E23">
-        <v>-25.50252459898593</v>
+        <v>-25.48900710407304</v>
       </c>
       <c r="F23">
-        <v>-4.109865492966586</v>
+        <v>-4.52736349234494</v>
       </c>
       <c r="G23">
-        <v>-6.136487952081113</v>
+        <v>-4.294367992209054</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-6.002021064591886</v>
       </c>
       <c r="E24">
-        <v>-26.06501541242668</v>
+        <v>-25.49073698114397</v>
       </c>
       <c r="F24">
-        <v>-4.0618748558528</v>
+        <v>-4.031567377686574</v>
       </c>
       <c r="G24">
-        <v>-6.377512220067752</v>
+        <v>-4.743526258249672</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-6.019994206469381</v>
       </c>
       <c r="E25">
-        <v>-25.76744032843465</v>
+        <v>-25.47035884810945</v>
       </c>
       <c r="F25">
-        <v>-3.882200309450781</v>
+        <v>-4.443067168701257</v>
       </c>
       <c r="G25">
-        <v>-6.569206048973711</v>
+        <v>-4.977793702790659</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-6.069615327747463</v>
       </c>
       <c r="E26">
-        <v>-26.49964023378685</v>
+        <v>-25.51019583395493</v>
       </c>
       <c r="F26">
-        <v>-3.167077357553191</v>
+        <v>-3.992589377915246</v>
       </c>
       <c r="G26">
-        <v>-6.470425991172937</v>
+        <v>-4.877510657315056</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-6.128024652421582</v>
       </c>
       <c r="E27">
-        <v>-27.0360923216835</v>
+        <v>-26.5066955962908</v>
       </c>
       <c r="F27">
-        <v>-3.880327370753052</v>
+        <v>-3.957491451058631</v>
       </c>
       <c r="G27">
-        <v>-7.656644116076892</v>
+        <v>-4.969464370213852</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-6.171622247275864</v>
       </c>
       <c r="E28">
-        <v>-25.77600820125716</v>
+        <v>-26.63257358828202</v>
       </c>
       <c r="F28">
-        <v>-3.54862835348706</v>
+        <v>-4.230860149289093</v>
       </c>
       <c r="G28">
-        <v>-7.776859956244447</v>
+        <v>-5.220026319899131</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-6.188456667295207</v>
       </c>
       <c r="E29">
-        <v>-26.51473816612843</v>
+        <v>-25.30594807078697</v>
       </c>
       <c r="F29">
-        <v>-3.760086528767092</v>
+        <v>-4.121269627000927</v>
       </c>
       <c r="G29">
-        <v>-7.531273756504692</v>
+        <v>-5.272697099428935</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-6.161534128355948</v>
       </c>
       <c r="E30">
-        <v>-26.33351769328948</v>
+        <v>-25.54658212260656</v>
       </c>
       <c r="F30">
-        <v>-3.92251612257763</v>
+        <v>-4.180690077538541</v>
       </c>
       <c r="G30">
-        <v>-6.798044198830293</v>
+        <v>-5.710331356447351</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.086699292609413</v>
       </c>
       <c r="E31">
-        <v>-25.27490085299038</v>
+        <v>-25.44666134362731</v>
       </c>
       <c r="F31">
-        <v>-3.759786659767279</v>
+        <v>-4.448005895156747</v>
       </c>
       <c r="G31">
-        <v>-7.179882521329831</v>
+        <v>-5.797815832868132</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.958826664165886</v>
       </c>
       <c r="E32">
-        <v>-24.92004510127532</v>
+        <v>-24.80264894110048</v>
       </c>
       <c r="F32">
-        <v>-3.68630384419974</v>
+        <v>-4.2255064107648</v>
       </c>
       <c r="G32">
-        <v>-7.042998084372046</v>
+        <v>-5.642163913248218</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.778104433487858</v>
       </c>
       <c r="E33">
-        <v>-24.71495051346794</v>
+        <v>-24.58625128216994</v>
       </c>
       <c r="F33">
-        <v>-3.886064643384841</v>
+        <v>-4.29826191975268</v>
       </c>
       <c r="G33">
-        <v>-6.638065396190552</v>
+        <v>-5.314942971055575</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.554847844281206</v>
       </c>
       <c r="E34">
-        <v>-22.86406356010489</v>
+        <v>-24.44930117122998</v>
       </c>
       <c r="F34">
-        <v>-4.133948618468176</v>
+        <v>-4.222274949526479</v>
       </c>
       <c r="G34">
-        <v>-6.808376411458358</v>
+        <v>-5.177350077352386</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.29665870884623</v>
       </c>
       <c r="E35">
-        <v>-24.10072641296356</v>
+        <v>-23.79637220338204</v>
       </c>
       <c r="F35">
-        <v>-4.240341642581536</v>
+        <v>-4.292909837963193</v>
       </c>
       <c r="G35">
-        <v>-7.372874084087184</v>
+        <v>-5.152458085442606</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.022953439270913</v>
       </c>
       <c r="E36">
-        <v>-23.51990886521376</v>
+        <v>-23.1440319371551</v>
       </c>
       <c r="F36">
-        <v>-3.77558196940386</v>
+        <v>-4.209917364611516</v>
       </c>
       <c r="G36">
-        <v>-6.506745986284281</v>
+        <v>-5.512748067027029</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.748239199150893</v>
       </c>
       <c r="E37">
-        <v>-24.51516329719754</v>
+        <v>-22.46647712765346</v>
       </c>
       <c r="F37">
-        <v>-4.194585940720502</v>
+        <v>-4.215990954408842</v>
       </c>
       <c r="G37">
-        <v>-6.444686499605104</v>
+        <v>-4.315072144011656</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.486417631169316</v>
       </c>
       <c r="E38">
-        <v>-22.14184441146559</v>
+        <v>-22.15922469470703</v>
       </c>
       <c r="F38">
-        <v>-3.854241252871492</v>
+        <v>-4.096962013933179</v>
       </c>
       <c r="G38">
-        <v>-6.291368514590376</v>
+        <v>-4.462967455433057</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.251855234846726</v>
       </c>
       <c r="E39">
-        <v>-21.79674752123707</v>
+        <v>-22.17472566123529</v>
       </c>
       <c r="F39">
-        <v>-3.936402873718161</v>
+        <v>-4.38400705798386</v>
       </c>
       <c r="G39">
-        <v>-6.125751852897257</v>
+        <v>-4.23719487074584</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.047944570431041</v>
       </c>
       <c r="E40">
-        <v>-22.67501788418069</v>
+        <v>-21.64423304513274</v>
       </c>
       <c r="F40">
-        <v>-4.337942375081583</v>
+        <v>-4.376694230551946</v>
       </c>
       <c r="G40">
-        <v>-5.791413237795181</v>
+        <v>-3.708133277569372</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.885853807456596</v>
       </c>
       <c r="E41">
-        <v>-21.79969102934205</v>
+        <v>-20.93942587905293</v>
       </c>
       <c r="F41">
-        <v>-4.220414436339792</v>
+        <v>-4.348509029671693</v>
       </c>
       <c r="G41">
-        <v>-5.510354542602136</v>
+        <v>-3.389844187241684</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.768243392041083</v>
       </c>
       <c r="E42">
-        <v>-19.6990089212419</v>
+        <v>-20.13929886358567</v>
       </c>
       <c r="F42">
-        <v>-3.950229154038288</v>
+        <v>-4.307963758774268</v>
       </c>
       <c r="G42">
-        <v>-5.86841321649309</v>
+        <v>-3.613627134059798</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.699155224693233</v>
       </c>
       <c r="E43">
-        <v>-19.39092324907806</v>
+        <v>-20.089313567489</v>
       </c>
       <c r="F43">
-        <v>-4.480458016528821</v>
+        <v>-4.292484885485557</v>
       </c>
       <c r="G43">
-        <v>-5.657528155095975</v>
+        <v>-3.275147026488094</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.682151834697966</v>
       </c>
       <c r="E44">
-        <v>-19.20165567792748</v>
+        <v>-19.04272888262829</v>
       </c>
       <c r="F44">
-        <v>-3.680773663418651</v>
+        <v>-4.369820437843516</v>
       </c>
       <c r="G44">
-        <v>-5.062801891148064</v>
+        <v>-2.876093867184345</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.711426605511614</v>
       </c>
       <c r="E45">
-        <v>-18.68748821062258</v>
+        <v>-18.72051890003453</v>
       </c>
       <c r="F45">
-        <v>-4.792885066168682</v>
+        <v>-4.272610694757591</v>
       </c>
       <c r="G45">
-        <v>-5.075550802019797</v>
+        <v>-3.512215192555304</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.788405985483217</v>
       </c>
       <c r="E46">
-        <v>-18.78182990962438</v>
+        <v>-17.75404292036951</v>
       </c>
       <c r="F46">
-        <v>-4.44327840238897</v>
+        <v>-4.331880382427896</v>
       </c>
       <c r="G46">
-        <v>-5.703518253727531</v>
+        <v>-3.185312062734431</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.903226817067484</v>
       </c>
       <c r="E47">
-        <v>-17.52582141580494</v>
+        <v>-17.52623803541365</v>
       </c>
       <c r="F47">
-        <v>-4.550859305357945</v>
+        <v>-4.555894122432161</v>
       </c>
       <c r="G47">
-        <v>-5.626495101210847</v>
+        <v>-3.238148369541199</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.051977219128882</v>
       </c>
       <c r="E48">
-        <v>-16.44935785944162</v>
+        <v>-16.73365998611717</v>
       </c>
       <c r="F48">
-        <v>-4.340357894428146</v>
+        <v>-4.74340750956687</v>
       </c>
       <c r="G48">
-        <v>-5.447851442820696</v>
+        <v>-2.716297144549265</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.22860243291889</v>
       </c>
       <c r="E49">
-        <v>-16.41655812220407</v>
+        <v>-16.64678121228002</v>
       </c>
       <c r="F49">
-        <v>-4.607783056543521</v>
+        <v>-4.686176434074856</v>
       </c>
       <c r="G49">
-        <v>-4.325252071544915</v>
+        <v>-3.130072299866152</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.42452612062826</v>
       </c>
       <c r="E50">
-        <v>-15.58256264963344</v>
+        <v>-15.59794134736349</v>
       </c>
       <c r="F50">
-        <v>-4.801692268395247</v>
+        <v>-4.677177050610841</v>
       </c>
       <c r="G50">
-        <v>-4.853932951984366</v>
+        <v>-3.261785664691596</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.641264234772828</v>
       </c>
       <c r="E51">
-        <v>-15.73404916213803</v>
+        <v>-15.23709442453628</v>
       </c>
       <c r="F51">
-        <v>-5.019354915522247</v>
+        <v>-4.815308971762465</v>
       </c>
       <c r="G51">
-        <v>-5.587516738031469</v>
+        <v>-3.073882410428102</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.871524671860644</v>
       </c>
       <c r="E52">
-        <v>-14.85111447096651</v>
+        <v>-14.54622137297808</v>
       </c>
       <c r="F52">
-        <v>-5.13372014752015</v>
+        <v>-4.876463195274138</v>
       </c>
       <c r="G52">
-        <v>-5.519498269381603</v>
+        <v>-3.240200907775547</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.119104520851074</v>
       </c>
       <c r="E53">
-        <v>-14.34557827512023</v>
+        <v>-13.68555771697628</v>
       </c>
       <c r="F53">
-        <v>-4.771712823720529</v>
+        <v>-4.690057335356971</v>
       </c>
       <c r="G53">
-        <v>-5.839260552474268</v>
+        <v>-3.449096331303559</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.384113478528649</v>
       </c>
       <c r="E54">
-        <v>-14.23885572818146</v>
+        <v>-13.87334900560036</v>
       </c>
       <c r="F54">
-        <v>-4.942961216901272</v>
+        <v>-4.878285603560297</v>
       </c>
       <c r="G54">
-        <v>-4.79173442239254</v>
+        <v>-3.394392876812642</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.667554626560226</v>
       </c>
       <c r="E55">
-        <v>-13.57503125187107</v>
+        <v>-13.23818976975853</v>
       </c>
       <c r="F55">
-        <v>-5.152636745530479</v>
+        <v>-5.004683700451265</v>
       </c>
       <c r="G55">
-        <v>-5.662196024306348</v>
+        <v>-3.75461333694074</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.97681311307979</v>
       </c>
       <c r="E56">
-        <v>-13.5824851200877</v>
+        <v>-12.48991378167909</v>
       </c>
       <c r="F56">
-        <v>-4.958218916093435</v>
+        <v>-5.080042768186145</v>
       </c>
       <c r="G56">
-        <v>-5.601788499851267</v>
+        <v>-3.652794198334916</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.306800533218587</v>
       </c>
       <c r="E57">
-        <v>-12.57110479216261</v>
+        <v>-11.96064838203262</v>
       </c>
       <c r="F57">
-        <v>-5.26742444490381</v>
+        <v>-5.159490657421243</v>
       </c>
       <c r="G57">
-        <v>-4.822548980272075</v>
+        <v>-3.401844914821542</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.662945064909909</v>
       </c>
       <c r="E58">
-        <v>-13.26944529735947</v>
+        <v>-11.24765826342095</v>
       </c>
       <c r="F58">
-        <v>-5.142106539106092</v>
+        <v>-5.338727825834582</v>
       </c>
       <c r="G58">
-        <v>-5.874686700290009</v>
+        <v>-3.251105844781907</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.038214890587725</v>
       </c>
       <c r="E59">
-        <v>-11.13558758867913</v>
+        <v>-10.72139071356756</v>
       </c>
       <c r="F59">
-        <v>-5.194724436531916</v>
+        <v>-5.054572955652269</v>
       </c>
       <c r="G59">
-        <v>-5.783573865958187</v>
+        <v>-3.428044572219334</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.426826364117661</v>
       </c>
       <c r="E60">
-        <v>-11.16824241474844</v>
+        <v>-11.21046590639595</v>
       </c>
       <c r="F60">
-        <v>-5.530827054911191</v>
+        <v>-5.297867775324094</v>
       </c>
       <c r="G60">
-        <v>-5.316406232183933</v>
+        <v>-3.226475385969729</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.828768056871005</v>
       </c>
       <c r="E61">
-        <v>-11.79930791008734</v>
+        <v>-10.51642745150639</v>
       </c>
       <c r="F61">
-        <v>-5.659945510352952</v>
+        <v>-5.064722113071368</v>
       </c>
       <c r="G61">
-        <v>-5.72514273719005</v>
+        <v>-3.557331307164492</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.23275298034147</v>
       </c>
       <c r="E62">
-        <v>-10.58903700374537</v>
+        <v>-10.59198956879838</v>
       </c>
       <c r="F62">
-        <v>-5.156084410660931</v>
+        <v>-5.423289227047162</v>
       </c>
       <c r="G62">
-        <v>-5.663526863613135</v>
+        <v>-4.054588489345181</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.642545846600534</v>
       </c>
       <c r="E63">
-        <v>-9.866985408644359</v>
+        <v>-10.79696641628157</v>
       </c>
       <c r="F63">
-        <v>-5.486823350107079</v>
+        <v>-5.324504757528516</v>
       </c>
       <c r="G63">
-        <v>-6.399474379175277</v>
+        <v>-4.43433785760944</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.048492436598153</v>
       </c>
       <c r="E64">
-        <v>-11.40958743698723</v>
+        <v>-9.718632600153079</v>
       </c>
       <c r="F64">
-        <v>-5.641004061320539</v>
+        <v>-5.536657933059496</v>
       </c>
       <c r="G64">
-        <v>-6.561144870585585</v>
+        <v>-4.055353225364753</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.444500095063887</v>
       </c>
       <c r="E65">
-        <v>-8.995992303431066</v>
+        <v>-9.210823110354948</v>
       </c>
       <c r="F65">
-        <v>-5.708284061775915</v>
+        <v>-5.209438726707845</v>
       </c>
       <c r="G65">
-        <v>-6.347588198938279</v>
+        <v>-4.292375043794412</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.827262677077183</v>
       </c>
       <c r="E66">
-        <v>-10.17464993272548</v>
+        <v>-9.051552151031174</v>
       </c>
       <c r="F66">
-        <v>-5.812880356992603</v>
+        <v>-5.49350496157806</v>
       </c>
       <c r="G66">
-        <v>-6.709778433662244</v>
+        <v>-4.80140452591275</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.18220145608634</v>
       </c>
       <c r="E67">
-        <v>-10.06649185952629</v>
+        <v>-8.66312229302325</v>
       </c>
       <c r="F67">
-        <v>-5.712762215955449</v>
+        <v>-5.444423364594786</v>
       </c>
       <c r="G67">
-        <v>-6.229957894836896</v>
+        <v>-4.511457015946762</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.50923195538253</v>
       </c>
       <c r="E68">
-        <v>-9.844737015844675</v>
+        <v>-9.195548567527077</v>
       </c>
       <c r="F68">
-        <v>-5.490543548113051</v>
+        <v>-5.441505026234723</v>
       </c>
       <c r="G68">
-        <v>-6.207151546616856</v>
+        <v>-4.389860678289331</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.79556889568139</v>
       </c>
       <c r="E69">
-        <v>-9.142637877221455</v>
+        <v>-8.034484059752458</v>
       </c>
       <c r="F69">
-        <v>-6.150429304857165</v>
+        <v>-5.567756502095396</v>
       </c>
       <c r="G69">
-        <v>-6.967931464269072</v>
+        <v>-4.737007794082847</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-11.0351442725088</v>
       </c>
       <c r="E70">
-        <v>-9.654849043755041</v>
+        <v>-8.339390743162911</v>
       </c>
       <c r="F70">
-        <v>-5.5845350838391</v>
+        <v>-5.62511183269783</v>
       </c>
       <c r="G70">
-        <v>-7.192138160916213</v>
+        <v>-4.875014505978445</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-11.22483188913881</v>
       </c>
       <c r="E71">
-        <v>-9.897819788162588</v>
+        <v>-8.993773351167308</v>
       </c>
       <c r="F71">
-        <v>-6.070296355779952</v>
+        <v>-5.676014181232458</v>
       </c>
       <c r="G71">
-        <v>-6.969235819211544</v>
+        <v>-4.779687347175131</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-11.35274994146388</v>
       </c>
       <c r="E72">
-        <v>-10.80614563309511</v>
+        <v>-9.333653439338999</v>
       </c>
       <c r="F72">
-        <v>-6.050442045869653</v>
+        <v>-5.623507285038608</v>
       </c>
       <c r="G72">
-        <v>-6.080112672092864</v>
+        <v>-4.802758539038313</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-11.42422642862912</v>
       </c>
       <c r="E73">
-        <v>-10.13700472829972</v>
+        <v>-8.946192674768715</v>
       </c>
       <c r="F73">
-        <v>-5.943534605599155</v>
+        <v>-5.815675268609648</v>
       </c>
       <c r="G73">
-        <v>-6.383712871862807</v>
+        <v>-4.547700868510703</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-11.43342951963683</v>
       </c>
       <c r="E74">
-        <v>-10.62212203484541</v>
+        <v>-9.178833969964765</v>
       </c>
       <c r="F74">
-        <v>-6.198693303213876</v>
+        <v>-5.678744480192084</v>
       </c>
       <c r="G74">
-        <v>-5.757235165647745</v>
+        <v>-4.48393976142434</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-11.38267642783295</v>
       </c>
       <c r="E75">
-        <v>-9.690048872216664</v>
+        <v>-8.931325694601533</v>
       </c>
       <c r="F75">
-        <v>-6.041002799314753</v>
+        <v>-5.922482476424408</v>
       </c>
       <c r="G75">
-        <v>-5.909553365909613</v>
+        <v>-4.341175795588809</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-11.27831089142685</v>
       </c>
       <c r="E76">
-        <v>-11.10223537761263</v>
+        <v>-10.49831808394971</v>
       </c>
       <c r="F76">
-        <v>-6.322544584524937</v>
+        <v>-6.10038845842145</v>
       </c>
       <c r="G76">
-        <v>-6.009339829554325</v>
+        <v>-3.90914298162284</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-11.11923225890965</v>
       </c>
       <c r="E77">
-        <v>-10.61289753329179</v>
+        <v>-9.947198268742225</v>
       </c>
       <c r="F77">
-        <v>-6.400624839178012</v>
+        <v>-5.85220130086869</v>
       </c>
       <c r="G77">
-        <v>-6.233678948023036</v>
+        <v>-3.693997248116685</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.9234631856731</v>
       </c>
       <c r="E78">
-        <v>-11.62090867655517</v>
+        <v>-11.04267235898975</v>
       </c>
       <c r="F78">
-        <v>-6.328804971171594</v>
+        <v>-6.145616490246899</v>
       </c>
       <c r="G78">
-        <v>-5.891636693451077</v>
+        <v>-3.846030741462175</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.69576362726473</v>
       </c>
       <c r="E79">
-        <v>-12.6061053677679</v>
+        <v>-11.24093800799357</v>
       </c>
       <c r="F79">
-        <v>-6.387264929705662</v>
+        <v>-6.284806236571898</v>
       </c>
       <c r="G79">
-        <v>-5.34944547666586</v>
+        <v>-3.457164130782763</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.4503490172947</v>
       </c>
       <c r="E80">
-        <v>-14.43132493045547</v>
+        <v>-11.72375484974337</v>
       </c>
       <c r="F80">
-        <v>-6.434497610645887</v>
+        <v>-6.440982484858703</v>
       </c>
       <c r="G80">
-        <v>-4.32886056618272</v>
+        <v>-3.304445354510644</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.20159243690055</v>
       </c>
       <c r="E81">
-        <v>-13.63852951440662</v>
+        <v>-12.31523242530722</v>
       </c>
       <c r="F81">
-        <v>-6.527424280075637</v>
+        <v>-6.129932181842294</v>
       </c>
       <c r="G81">
-        <v>-4.862669481662503</v>
+        <v>-3.186040382753071</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.951721848889534</v>
       </c>
       <c r="E82">
-        <v>-13.85513548314151</v>
+        <v>-13.17028983048752</v>
       </c>
       <c r="F82">
-        <v>-6.502726920144871</v>
+        <v>-6.479369030304432</v>
       </c>
       <c r="G82">
-        <v>-5.088160669978882</v>
+        <v>-3.375790921427478</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.719905753769273</v>
       </c>
       <c r="E83">
-        <v>-15.52396419597419</v>
+        <v>-14.67088120546123</v>
       </c>
       <c r="F83">
-        <v>-6.892026464764527</v>
+        <v>-6.968658319013808</v>
       </c>
       <c r="G83">
-        <v>-5.204857400238191</v>
+        <v>-2.55151805087758</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.507757361790286</v>
       </c>
       <c r="E84">
-        <v>-15.61438423648534</v>
+        <v>-14.3809818849122</v>
       </c>
       <c r="F84">
-        <v>-6.629392165523242</v>
+        <v>-6.712194942739678</v>
       </c>
       <c r="G84">
-        <v>-4.629279331689424</v>
+        <v>-3.195210593896852</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.32820129180157</v>
       </c>
       <c r="E85">
-        <v>-16.75414680252788</v>
+        <v>-15.68859234004903</v>
       </c>
       <c r="F85">
-        <v>-7.020602753741156</v>
+        <v>-7.228684917671079</v>
       </c>
       <c r="G85">
-        <v>-4.285859890173127</v>
+        <v>-2.928519666344244</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-9.189323708546739</v>
       </c>
       <c r="E86">
-        <v>-18.62148570196079</v>
+        <v>-16.9261382453392</v>
       </c>
       <c r="F86">
-        <v>-7.299985813499644</v>
+        <v>-6.687242031465148</v>
       </c>
       <c r="G86">
-        <v>-4.399454639262139</v>
+        <v>-2.102876229941088</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-9.088494568101686</v>
       </c>
       <c r="E87">
-        <v>-19.75767077353726</v>
+        <v>-18.62917505082581</v>
       </c>
       <c r="F87">
-        <v>-7.149081295364256</v>
+        <v>-6.925859060413366</v>
       </c>
       <c r="G87">
-        <v>-3.77909813174919</v>
+        <v>-1.842481960004174</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-9.036169096289656</v>
       </c>
       <c r="E88">
-        <v>-20.54454294558407</v>
+        <v>-19.66751338451855</v>
       </c>
       <c r="F88">
-        <v>-7.180760549949516</v>
+        <v>-6.920771227825371</v>
       </c>
       <c r="G88">
-        <v>-4.256498661785331</v>
+        <v>-1.898407005799082</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-9.023702997353498</v>
       </c>
       <c r="E89">
-        <v>-21.59354130709087</v>
+        <v>-20.45843854080223</v>
       </c>
       <c r="F89">
-        <v>-7.514426525613456</v>
+        <v>-6.91527003990338</v>
       </c>
       <c r="G89">
-        <v>-4.009988819840119</v>
+        <v>-2.062653101638944</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.056415895891314</v>
       </c>
       <c r="E90">
-        <v>-23.81464459600299</v>
+        <v>-22.59346006730254</v>
       </c>
       <c r="F90">
-        <v>-7.418278335354219</v>
+        <v>-7.13408660282248</v>
       </c>
       <c r="G90">
-        <v>-4.971146127347802</v>
+        <v>-2.489438700925167</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-9.129296910714492</v>
       </c>
       <c r="E91">
-        <v>-24.84913372678922</v>
+        <v>-24.96048890263783</v>
       </c>
       <c r="F91">
-        <v>-7.28958358983899</v>
+        <v>-7.05301925531491</v>
       </c>
       <c r="G91">
-        <v>-3.658832633398546</v>
+        <v>-2.984242768861257</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.231310840453551</v>
       </c>
       <c r="E92">
-        <v>-27.71164101719975</v>
+        <v>-26.11506410715945</v>
       </c>
       <c r="F92">
-        <v>-7.490420852464028</v>
+        <v>-7.3417831617264</v>
       </c>
       <c r="G92">
-        <v>-5.027230079328595</v>
+        <v>-2.679619610519679</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.361085371624931</v>
       </c>
       <c r="E93">
-        <v>-29.6986765416034</v>
+        <v>-28.27934410422333</v>
       </c>
       <c r="F93">
-        <v>-7.480615053333389</v>
+        <v>-7.176333754548956</v>
       </c>
       <c r="G93">
-        <v>-5.082204998553732</v>
+        <v>-2.657465439770876</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.498360817519849</v>
       </c>
       <c r="E94">
-        <v>-31.57260889919148</v>
+        <v>-30.25443804266875</v>
       </c>
       <c r="F94">
-        <v>-7.851218759855561</v>
+        <v>-7.029831594975746</v>
       </c>
       <c r="G94">
-        <v>-4.586748753146407</v>
+        <v>-3.092676377454545</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.638434386748083</v>
       </c>
       <c r="E95">
-        <v>-34.32076995667133</v>
+        <v>-32.89199791522227</v>
       </c>
       <c r="F95">
-        <v>-7.304709578614109</v>
+        <v>-6.899872346620143</v>
       </c>
       <c r="G95">
-        <v>-6.78924476878691</v>
+        <v>-3.677639842607146</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.762135096969221</v>
       </c>
       <c r="E96">
-        <v>-36.13484947330003</v>
+        <v>-35.19046112560742</v>
       </c>
       <c r="F96">
-        <v>-7.396726286451883</v>
+        <v>-7.05746965918645</v>
       </c>
       <c r="G96">
-        <v>-6.212441798388612</v>
+        <v>-4.380988416244084</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.855364291051311</v>
       </c>
       <c r="E97">
-        <v>-37.87225966074187</v>
+        <v>-38.07854070873927</v>
       </c>
       <c r="F97">
-        <v>-7.468361014343776</v>
+        <v>-7.04692992653693</v>
       </c>
       <c r="G97">
-        <v>-6.599269113015833</v>
+        <v>-4.700658004061649</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.908188716755685</v>
       </c>
       <c r="E98">
-        <v>-40.53310494664282</v>
+        <v>-40.00674229883527</v>
       </c>
       <c r="F98">
-        <v>-7.932559882789757</v>
+        <v>-6.857551056011116</v>
       </c>
       <c r="G98">
-        <v>-7.024025347886483</v>
+        <v>-5.271071621569154</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-9.912372302283059</v>
       </c>
       <c r="E99">
-        <v>-43.33735341894468</v>
+        <v>-42.52297529577528</v>
       </c>
       <c r="F99">
-        <v>-7.752635169432093</v>
+        <v>-6.820429427589461</v>
       </c>
       <c r="G99">
-        <v>-6.740993567552032</v>
+        <v>-6.096741542336623</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-9.862501440670139</v>
       </c>
       <c r="E100">
-        <v>-44.35721784292313</v>
+        <v>-45.5003088373613</v>
       </c>
       <c r="F100">
-        <v>-8.059720491875002</v>
+        <v>-6.858895910489561</v>
       </c>
       <c r="G100">
-        <v>-7.942115768473786</v>
+        <v>-6.332396105458564</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-9.776095017043508</v>
       </c>
       <c r="E101">
-        <v>-47.87536439287519</v>
+        <v>-47.29374983370005</v>
       </c>
       <c r="F101">
-        <v>-8.081519394263372</v>
+        <v>-6.861546271994817</v>
       </c>
       <c r="G101">
-        <v>-8.488167081357794</v>
+        <v>-6.455442462062195</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.630388048946132</v>
       </c>
       <c r="E102">
-        <v>-50.33370537810114</v>
+        <v>-49.50994878526186</v>
       </c>
       <c r="F102">
-        <v>-7.66092951355407</v>
+        <v>-6.508565253599802</v>
       </c>
       <c r="G102">
-        <v>-9.008876168138681</v>
+        <v>-7.370944036037789</v>
       </c>
     </row>
   </sheetData>
